--- a/outputs/tables/tabla_contraste_anual.xlsx
+++ b/outputs/tables/tabla_contraste_anual.xlsx
@@ -49,7 +49,7 @@
     <t>Línea base cantonal de referencia (2024)</t>
   </si>
   <si>
-    <t>Variación neta estimada de +37.1% en la tasa de homicidios en 2025 frente a 2024</t>
+    <t>Variación neta estimada de +37.7% en la tasa de homicidios en 2025 frente a 2024</t>
   </si>
 </sst>
 </file>
@@ -479,28 +479,28 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>0.3175</v>
+        <v>0.3207</v>
       </c>
       <c r="C3">
-        <v>0.3157</v>
+        <v>0.3201</v>
       </c>
       <c r="D3">
-        <v>0.1995</v>
+        <v>0.2521</v>
       </c>
       <c r="E3">
-        <v>0.4422</v>
+        <v>0.3922</v>
       </c>
       <c r="F3">
-        <v>1.3763</v>
+        <v>1.379</v>
       </c>
       <c r="G3">
-        <v>1.3712</v>
+        <v>1.3772</v>
       </c>
       <c r="H3">
-        <v>1.2208</v>
+        <v>1.2868</v>
       </c>
       <c r="I3">
-        <v>1.5561</v>
+        <v>1.4803</v>
       </c>
       <c r="J3" t="s">
         <v>11</v>
